--- a/artfynd/A 33243-2024 artfynd.xlsx
+++ b/artfynd/A 33243-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651755</v>
+        <v>119651760</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515118</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>7136078</v>
+        <v>7136134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651750</v>
+        <v>119651752</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515011</v>
+        <v>515111</v>
       </c>
       <c r="R3" t="n">
-        <v>7136238</v>
+        <v>7136070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651752</v>
+        <v>119651755</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515111</v>
+        <v>515118</v>
       </c>
       <c r="R5" t="n">
-        <v>7136070</v>
+        <v>7136078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651760</v>
+        <v>119651748</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515053</v>
+        <v>514962</v>
       </c>
       <c r="R6" t="n">
-        <v>7136134</v>
+        <v>7136324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651749</v>
+        <v>119651751</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515090</v>
+        <v>515023</v>
       </c>
       <c r="R7" t="n">
-        <v>7136038</v>
+        <v>7136175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651748</v>
+        <v>119651749</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514962</v>
+        <v>515090</v>
       </c>
       <c r="R8" t="n">
-        <v>7136324</v>
+        <v>7136038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651751</v>
+        <v>119651750</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515023</v>
+        <v>515011</v>
       </c>
       <c r="R9" t="n">
-        <v>7136175</v>
+        <v>7136238</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33243-2024 artfynd.xlsx
+++ b/artfynd/A 33243-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651760</v>
+        <v>119651755</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515118</v>
       </c>
       <c r="R2" t="n">
-        <v>7136134</v>
+        <v>7136078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651752</v>
+        <v>119651751</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515111</v>
+        <v>515023</v>
       </c>
       <c r="R3" t="n">
-        <v>7136070</v>
+        <v>7136175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651759</v>
+        <v>119651760</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515010</v>
+        <v>515053</v>
       </c>
       <c r="R4" t="n">
-        <v>7136173</v>
+        <v>7136134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651755</v>
+        <v>119651759</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515118</v>
+        <v>515010</v>
       </c>
       <c r="R5" t="n">
-        <v>7136078</v>
+        <v>7136173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651748</v>
+        <v>119651752</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514962</v>
+        <v>515111</v>
       </c>
       <c r="R6" t="n">
-        <v>7136324</v>
+        <v>7136070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651751</v>
+        <v>119651749</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515023</v>
+        <v>515090</v>
       </c>
       <c r="R7" t="n">
-        <v>7136175</v>
+        <v>7136038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651749</v>
+        <v>119651748</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515090</v>
+        <v>514962</v>
       </c>
       <c r="R8" t="n">
-        <v>7136038</v>
+        <v>7136324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 33243-2024 artfynd.xlsx
+++ b/artfynd/A 33243-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651755</v>
+        <v>119651752</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515118</v>
+        <v>515111</v>
       </c>
       <c r="R2" t="n">
-        <v>7136078</v>
+        <v>7136070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651751</v>
+        <v>119651748</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515023</v>
+        <v>514962</v>
       </c>
       <c r="R3" t="n">
-        <v>7136175</v>
+        <v>7136324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651760</v>
+        <v>119651749</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515053</v>
+        <v>515090</v>
       </c>
       <c r="R4" t="n">
-        <v>7136134</v>
+        <v>7136038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651759</v>
+        <v>119651751</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515010</v>
+        <v>515023</v>
       </c>
       <c r="R5" t="n">
-        <v>7136173</v>
+        <v>7136175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651752</v>
+        <v>119651759</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515111</v>
+        <v>515010</v>
       </c>
       <c r="R6" t="n">
-        <v>7136070</v>
+        <v>7136173</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651749</v>
+        <v>119651755</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515090</v>
+        <v>515118</v>
       </c>
       <c r="R7" t="n">
-        <v>7136038</v>
+        <v>7136078</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651748</v>
+        <v>119651750</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514962</v>
+        <v>515011</v>
       </c>
       <c r="R8" t="n">
-        <v>7136324</v>
+        <v>7136238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651750</v>
+        <v>119651760</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515011</v>
+        <v>515053</v>
       </c>
       <c r="R9" t="n">
-        <v>7136238</v>
+        <v>7136134</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33243-2024 artfynd.xlsx
+++ b/artfynd/A 33243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651752</v>
+        <v>119651759</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515111</v>
+        <v>515010</v>
       </c>
       <c r="R2" t="n">
-        <v>7136070</v>
+        <v>7136173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651748</v>
+        <v>119651760</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514962</v>
+        <v>515053</v>
       </c>
       <c r="R3" t="n">
-        <v>7136324</v>
+        <v>7136134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,16 +845,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651749</v>
+        <v>119651748</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515090</v>
+        <v>514962</v>
       </c>
       <c r="R4" t="n">
-        <v>7136038</v>
+        <v>7136324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,14 +944,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -996,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651751</v>
+        <v>119651749</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515023</v>
+        <v>515090</v>
       </c>
       <c r="R5" t="n">
-        <v>7136175</v>
+        <v>7136038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651759</v>
+        <v>119651750</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515010</v>
+        <v>515011</v>
       </c>
       <c r="R6" t="n">
-        <v>7136173</v>
+        <v>7136238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651755</v>
+        <v>119651751</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515118</v>
+        <v>515023</v>
       </c>
       <c r="R7" t="n">
-        <v>7136078</v>
+        <v>7136175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651750</v>
+        <v>119651752</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515011</v>
+        <v>515111</v>
       </c>
       <c r="R8" t="n">
-        <v>7136238</v>
+        <v>7136070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,108 +1376,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>119651760</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Harrsjöberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>515053</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7136134</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33243-2024 artfynd.xlsx
+++ b/artfynd/A 33243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651748</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651749</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651750</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651751</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,8 +1411,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651752</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>